--- a/Nifty50_Upcoming_Quarterly_Result_Dates_2026.xlsx
+++ b/Nifty50_Upcoming_Quarterly_Result_Dates_2026.xlsx
@@ -1642,22 +1642,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Expected: 18-Oct</t>
+          <t>15-Oct-2026</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Pending Announcement (Est: Oct-Nov)</t>
+          <t>ANNOUNCED ON NSE ✅</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Q2 FY27 Financial Results (Period ended Sept 30)</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Historically announced around 18-Oct</t>
+          <t>To consider and approve the unaudited financial results for the quarter and half year ended September 30, 2026</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1732,22 +1732,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Expected: 19-Oct</t>
+          <t>24-Oct-2026</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Pending Announcement (Est: Oct-Nov)</t>
+          <t>ANNOUNCED ON NSE ✅</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Q2 FY27 Financial Results (Period ended Sept 30)</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Historically announced around 19-Oct</t>
+          <t>To consider and approve the Standalone and Consolidated Unaudited Financial Results for the quarter and half year ended September 30, 2026</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
